--- a/markets/prospects/UAE_Fashion_Prospects.xlsx
+++ b/markets/prospects/UAE_Fashion_Prospects.xlsx
@@ -519,12 +519,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Company Phone Numbers (comma separated)</t>
+          <t>Company Phone Numbers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Company Emails (comma separated; marketing/sales/business only)</t>
+          <t>Company Emails</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">

--- a/markets/prospects/UAE_Fashion_Prospects.xlsx
+++ b/markets/prospects/UAE_Fashion_Prospects.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Prospects'!$A$1:$J$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Jessica Carr</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ecommerce Manager (PrettyLittleThing group, UK)</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Benedicte Blanc</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager Omnichannel Distribution (Swarovski &amp; Michael Kors), Chalhoub Group</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>VP, CDO - Omnichannel Digital Innovation, Al Tayer Insignia (Saint Laurent UAE franchise partner)</t>
         </is>
       </c>
     </row>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>VP, CDO - Omnichannel Digital Innovation, Al Tayer Insignia (Balenciaga UAE franchise partner)</t>
         </is>
       </c>
     </row>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Nikita Shetye</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager - GCC eCommerce, Club L London (Dubai)</t>
         </is>
       </c>
     </row>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Zahiya Hassan Tawil</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing and Communications, Valentino (Dubai)</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Imran K.</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Lead (Sharaf Retail - Adventure HQ)</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Patrick McMahon</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ecommerce Lead - Tory Burch, Chalhoub Group (Dubai)</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ilaria Manzi</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital Manager (Maison Margiela, Marni, Jil Sander - OTB/Chalhoub JV), OTB</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rania Masri El Khatib</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3748,12 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ahmed Ismail</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional Head of E-Commerce, Jashanmal Group (Reiss UAE franchise operator)</t>
         </is>
       </c>
     </row>
@@ -3837,19 +3837,19 @@
           <t>info@casbasics.com</t>
         </is>
       </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/crystal-abaya-studio</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Maryam Karim</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>CEO, Crystal Abaya Studio (CAS Abaya)</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>+971506172781, WhatsApp +971506172781</t>
+          <t>+971506172781, WhatsApp +971506172781, +971 2 5059999</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@liwastores.com</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rebecca Holland</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Digital, Liwa Trading Enterprises (GANT UAE franchise operator)</t>
         </is>
       </c>
     </row>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Maria ElKheyami</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager - omni-channel fashion franchise (incl. Off-White), Chalhoub Group</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Vinay Banga</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Brand (Columbia, GCC &amp; SEA), GMG</t>
         </is>
       </c>
     </row>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Kenza Bouzoubaa</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional E-commerce Manager, Max Mara Fashion Group (Dubai)</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Alessandro Bovone</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Omnichannel Senior Manager EMR+ (eCommerce &amp; Digital), HUGO BOSS</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hema Subramanian</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Senior Manager - Performance Marketing &amp; Ecommerce P&amp;L, H&amp;M/COS (Alshaya Group)</t>
         </is>
       </c>
     </row>
@@ -4228,12 +4228,12 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hammad Sohail</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Marketing &amp; Strategy Officer, Maria.B. Designs</t>
         </is>
       </c>
     </row>
@@ -4276,12 +4276,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Muhammad Hamza Muzaffar</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of eCommerce &amp; Digital (Tryano), Chalhoub Group</t>
         </is>
       </c>
     </row>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rema Nelson</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, Fashion MENA (Maje, Sandro, Kiabi, Ted Baker, Aape), Al-Futtaim</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shames Al Hashemi</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Managing Director, Dual Investments LLC (Suitsupply UAE franchise partner)</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Kunal Singh</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Digital Commerce &amp; Transformation, Liwa Trading Enterprises (La Senza UAE franchise operator)</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Tarek Barakat</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing &amp; E-commerce Director, Beside Group (Diesel Middle East partner)</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Phillip Smith</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (Allbirds and other brands)</t>
         </is>
       </c>
     </row>
@@ -4564,12 +4564,12 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Phillip Smith</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (DKNY and other brands)</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ingie Chalhoub</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder and President, Etoile Group (Etoile La Boutique)</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sara AlQenaei</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional Marketing Manager - Lacoste Middle East, Chalhoub Group</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Stuart Taylor</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager (PGA Professional), Prosports International - Golf Superstore</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dean Cheesley</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>CEO &amp; Founder, eGolf Megastore</t>
         </is>
       </c>
     </row>
@@ -5000,12 +5000,12 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Waleed Ali Mousa</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Creative Director, Posh Abaya</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ashwani Saklani</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Senior Marketing Manager (Crocs, Aeropostale, LC Waikiki; e-commerce marketing), Apparel Group</t>
         </is>
       </c>
     </row>
@@ -5240,12 +5240,12 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Keeman Au</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of E-Commerce, KARL LAGERFELD (global e-commerce, Amsterdam)</t>
         </is>
       </c>
     </row>
@@ -5425,19 +5425,19 @@
           <t>online@amri.ae</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/amri-fashions</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Darshak Jayesh Khandhar</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of E-commerce Business Development - B2B &amp; Private Labels, Amri Fashions (remote, Canada)</t>
         </is>
       </c>
     </row>
@@ -5480,12 +5480,12 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mustahsin Qamar</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director, BATIK (Dubai)</t>
         </is>
       </c>
     </row>
@@ -5576,12 +5576,12 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Erkal Ceyhan</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of Ecommerce, Ipekyol Group (runs ae.ipekyol.com)</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Yazan Ashkar</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Global CRM Director, ELIE SAAB (Dubai)</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5672,12 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Candice de Dieuleveult</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of Ecommerce, GMG (operator of JD Sports Middle East)</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rahul Jagtiani</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Group Director - Digital (leads e-commerce, IT, analytics, loyalty), Landmark Group</t>
         </is>
       </c>
     </row>
@@ -5818,12 +5818,12 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>David Hunt</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Co-Owner, Sported.ae</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Muhammed Hashim</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing &amp; Omni Channel Manager (E-commerce &amp; Marketing for D'S Damat &amp; Damat Tween UAE), Nahr Al Madeena Trading LLC</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Phillip Smith</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (Triumph and other brands)</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rishi Udainiya</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Operations Manager (oversees company website), RR Cellars LLC</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ahmed Abuelela</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>International E-Commerce Director - MENA &amp; CIS, DeFacto (Istanbul)</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Seifollah Nouraei</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Owner and CEO, Habayeb</t>
         </is>
       </c>
     </row>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Muhammed Sagar</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital &amp; E-Commerce Lead (Head of Digital), Seventy8 Sports Trading LLC - Official Liverpool FC Store Middle East</t>
         </is>
       </c>
     </row>
@@ -6254,88 +6254,90 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6348,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8028,22 +8030,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Decathlon</t>
+          <t>PrettyLittleThing</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>https://decathlon.ae/</t>
+          <t>https://www.prettylittlething.ae/</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Jessica Carr</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
+          <t>Ecommerce Manager (PrettyLittleThing group; UK-based)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8058,7 +8060,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://linkedin.com/in/jessica-carr-673712114</t>
         </is>
       </c>
     </row>
@@ -8075,12 +8077,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Mohammed Sajjad</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
+          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -8095,7 +8097,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sajbhojani</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
@@ -8112,12 +8114,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Mohammed Sajjad</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
+          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8132,7 +8134,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://www.linkedin.com/in/sajbhojani</t>
         </is>
       </c>
     </row>
@@ -8149,12 +8151,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Kassem Haidar</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
+          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -8169,29 +8171,29 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Bloomingdale's</t>
+          <t>Decathlon</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>https://bloomingdales.ae/</t>
+          <t>https://decathlon.ae/</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Sumit Srivastava</t>
+          <t>Kassem Haidar</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
+          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8206,7 +8208,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
+          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
         </is>
       </c>
     </row>
@@ -8223,12 +8225,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Nour Salameh</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager, Al Tayer Insignia (ex Bloomingdale's digital)</t>
+          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -8243,29 +8245,29 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/nour-salameh</t>
+          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Bloomingdale's</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>https://www.underarmour.ae/en/</t>
+          <t>https://bloomingdales.ae/</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Douglas Harvey</t>
+          <t>Nour Salameh</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Vice President - Digital &amp; Omni, GMG</t>
+          <t>Digital Marketing Manager, Al Tayer Insignia (ex Bloomingdale's digital)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8280,7 +8282,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/douglas-harvey-45bb6354</t>
+          <t>https://linkedin.com/in/nour-salameh</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8299,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Mohammed Abdul Qadir</t>
+          <t>Douglas Harvey</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Head of Category - Sun &amp; Sand Sports, Columbia.com, Vans.com, GMG (launched underarmour.com UAE/KSA)</t>
+          <t>Vice President - Digital &amp; Omni, GMG</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -8317,29 +8319,29 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohammed-abdul-qadir-b0525755</t>
+          <t>https://linkedin.com/in/douglas-harvey-45bb6354</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>victoriassecret</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>https://www.victoriassecret.com/ae/</t>
+          <t>https://www.underarmour.ae/en/</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Mohammed Abdul Qadir</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group</t>
+          <t>Head of Category - Sun &amp; Sand Sports, Columbia.com, Vans.com, GMG (launched underarmour.com UAE/KSA)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8354,7 +8356,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/robsilsbury</t>
+          <t>https://www.linkedin.com/in/mohammed-abdul-qadir-b0525755</t>
         </is>
       </c>
     </row>
@@ -8371,12 +8373,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Maelle Mandjee</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Vice President Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -8391,29 +8393,29 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ma%C3%ABlle-basselot</t>
+          <t>https://linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>victoriassecret</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>https://www.splashfashions.com/ae/</t>
+          <t>https://www.victoriassecret.com/ae/</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Richard Marriott</t>
+          <t>Maelle Mandjee</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Chief Digital Officer, Landmark Group</t>
+          <t>Director of Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -8428,7 +8430,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/richardkmarriott</t>
+          <t>https://linkedin.com/in/ma%C3%ABlle-basselot</t>
         </is>
       </c>
     </row>
@@ -8445,12 +8447,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Derrick Pereira</t>
+          <t>Richard Marriott</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Vice President &amp; Head of Product (Ecommerce), Landmark Group</t>
+          <t>Chief Digital Officer, Landmark Group</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -8465,7 +8467,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/derrickpereira</t>
+          <t>https://linkedin.com/in/richardkmarriott</t>
         </is>
       </c>
     </row>
@@ -8482,12 +8484,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Rahul Jagtiani</t>
+          <t>Derrick Pereira</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Group Director - Digital (investments lead), Landmark Group</t>
+          <t>Vice President &amp; Head of Product (Ecommerce), Landmark Group</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -8502,7 +8504,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/rahul-jagtiani-b8b278177</t>
+          <t>https://linkedin.com/in/derrickpereira</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8521,12 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Kabir Lumba</t>
+          <t>Rahul Jagtiani</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>CEO, Landmark Retail Brands</t>
+          <t>Group Director - Digital (investments lead), Landmark Group</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -8537,31 +8539,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/rahul-jagtiani-b8b278177</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Jashanmal</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>https://www.jashanmal.com/</t>
+          <t>https://www.splashfashions.com/ae/</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Ahmed Ismail</t>
+          <t>Kabir Lumba</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of E-Commerce, Jashanmal Group</t>
+          <t>CEO, Landmark Retail Brands</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -8574,9 +8576,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ahmed-ismail-899350a2</t>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8595,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Bismil Razik</t>
+          <t>Ahmed Ismail</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager, Jashanmal Group</t>
+          <t>Regional Head of E-Commerce, Jashanmal Group</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -8613,29 +8615,29 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/bismilrazik</t>
+          <t>https://www.linkedin.com/in/ahmed-ismail-899350a2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>On UAE (Mizzen General Trading LLC, Seddiqi Holding)</t>
+          <t>Jashanmal</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>https://on.ae/</t>
+          <t>https://www.jashanmal.com/</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Hassan Abdulmagied Seddiqi</t>
+          <t>Bismil Razik</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CEO, Mizzen (Seddiqi Holding) - operator of On.ae</t>
+          <t>Digital Marketing Manager, Jashanmal Group</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -8648,31 +8650,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bismilrazik</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>PUMA</t>
+          <t>On UAE (Mizzen General Trading LLC, Seddiqi Holding)</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>https://ae.puma.com/ae/</t>
+          <t>https://on.ae/</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Toby Walker</t>
+          <t>Hassan Abdulmagied Seddiqi</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Director Retail &amp; Ecommerce GCC, PUMA Middle East</t>
+          <t>CEO, Mizzen (Seddiqi Holding) - operator of On.ae</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -8685,9 +8687,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/tobywalker1</t>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8706,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Miroslav Ryba</t>
+          <t>Toby Walker</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Managing Director GCC &amp; CIS, PUMA Group</t>
+          <t>Director Retail &amp; Ecommerce GCC, PUMA Middle East</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -8724,7 +8726,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/miroslav-ryba-34a9555</t>
+          <t>https://www.linkedin.com/in/tobywalker1</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8743,12 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Amel Nefzaoui</t>
+          <t>Miroslav Ryba</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Head of Business Solutions &amp; Strategy GCC, PUMA Middle East</t>
+          <t>Managing Director GCC &amp; CIS, PUMA Group</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -8761,29 +8763,29 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ameln</t>
+          <t>https://www.linkedin.com/in/miroslav-ryba-34a9555</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Guess UAE</t>
+          <t>PUMA</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>https://www.guess.ae/</t>
+          <t>https://ae.puma.com/ae/</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Darine Sabbagh</t>
+          <t>Amel Nefzaoui</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>General Manager E-commerce &amp; Omnichannel, Chalhoub Group</t>
+          <t>Head of Business Solutions &amp; Strategy GCC, PUMA Middle East</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -8798,7 +8800,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/sdarine</t>
+          <t>https://www.linkedin.com/in/ameln</t>
         </is>
       </c>
     </row>
@@ -8815,12 +8817,12 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Katherine Cabanach Dresden</t>
+          <t>Darine Sabbagh</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>District Manager / Market manager ME, GUESS? (Guess Europe Sagl)</t>
+          <t>General Manager E-commerce &amp; Omnichannel, Chalhoub Group</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -8835,29 +8837,29 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/katherinecabanach</t>
+          <t>https://linkedin.com/in/sdarine</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Calvin Klein</t>
+          <t>Guess UAE</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>https://www.calvinklein.ae/</t>
+          <t>https://www.guess.ae/</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Plama Spetsova</t>
+          <t>Katherine Cabanach Dresden</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>General Manager, Digital Commerce &amp; Technology, Apparel Group</t>
+          <t>District Manager / Market manager ME, GUESS? (Guess Europe Sagl)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -8872,7 +8874,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/plama-spetsova</t>
+          <t>https://linkedin.com/in/katherinecabanach</t>
         </is>
       </c>
     </row>
@@ -8889,12 +8891,12 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Vikas Joon</t>
+          <t>Plama Spetsova</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Director of Ecommerce - Category Management, Merchandising &amp; Planning, Apparel Group</t>
+          <t>General Manager, Digital Commerce &amp; Technology, Apparel Group</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -8909,7 +8911,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/vikasjoon</t>
+          <t>https://linkedin.com/in/plama-spetsova</t>
         </is>
       </c>
     </row>
@@ -8926,12 +8928,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Ahmed Khorshed</t>
+          <t>Vikas Joon</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Group Head of Digital Marketing - Ecommerce, Apparel Group</t>
+          <t>Director of Ecommerce - Category Management, Merchandising &amp; Planning, Apparel Group</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -8946,7 +8948,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ahmedkhorshed</t>
+          <t>https://linkedin.com/in/vikasjoon</t>
         </is>
       </c>
     </row>
@@ -8963,12 +8965,12 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Manbeer Singh</t>
+          <t>Ahmed Khorshed</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Lead Ecommerce Manager, Apparel Group</t>
+          <t>Group Head of Digital Marketing - Ecommerce, Apparel Group</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -8983,29 +8985,29 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/manbeer-singh</t>
+          <t>https://linkedin.com/in/ahmedkhorshed</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Al Telal Gents Fashion</t>
+          <t>Calvin Klein</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>https://altelal.com/</t>
+          <t>https://www.calvinklein.ae/</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Hassan Abdussalam</t>
+          <t>Manbeer Singh</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CEO, Telal Gents Fashion</t>
+          <t>Lead Ecommerce Manager, Apparel Group</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -9020,7 +9022,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hassanthurab</t>
+          <t>https://linkedin.com/in/manbeer-singh</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9039,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Jamshir KP</t>
+          <t>Hassan Abdussalam</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Marketing Manager, Telal Gents Fashion</t>
+          <t>CEO, Telal Gents Fashion</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -9057,29 +9059,29 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jamshir-kp-1a526665</t>
+          <t>https://www.linkedin.com/in/hassanthurab</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Primark UAE (Alshaya Group, franchise operator)</t>
+          <t>Al Telal Gents Fashion</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>https://www.primark.ae/en/</t>
+          <t>https://altelal.com/</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Jamshir KP</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Marketing Manager, Telal Gents Fashion</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -9094,7 +9096,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://www.linkedin.com/in/jamshir-kp-1a526665</t>
         </is>
       </c>
     </row>
@@ -9111,12 +9113,12 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Ghansham Pindoria</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Vice President, Primark Middle East</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -9129,31 +9131,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>victoriassecret</t>
+          <t>Primark UAE (Alshaya Group, franchise operator)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>https://www.victoriassecret.ae/</t>
+          <t>https://www.primark.ae/en/</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Ghansham Pindoria</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group</t>
+          <t>Vice President, Primark Middle East</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -9166,9 +9168,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/robsilsbury</t>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -9185,12 +9187,12 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Maelle Mandjee</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Vice President Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -9205,29 +9207,29 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ma%C3%ABlle-basselot</t>
+          <t>https://linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>victoriassecret</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>https://www.gymshark.ae/</t>
+          <t>https://www.victoriassecret.ae/</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Sumit Srivastava</t>
+          <t>Maelle Mandjee</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
+          <t>Director of Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -9242,29 +9244,29 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
+          <t>https://linkedin.com/in/ma%C3%ABlle-basselot</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>Michael Kors UAE</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>https://www.gymshark.ae/</t>
+          <t>https://www.michaelkors.ae/</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Nour Salameh</t>
+          <t>Benedicte Blanc</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager, Al Tayer Insignia (ex Bloomingdale's digital)</t>
+          <t>General Manager Omnichannel Distribution (Swarovski &amp; Michael Kors), Chalhoub Group</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -9279,29 +9281,29 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/nour-salameh</t>
+          <t>https://linkedin.com/in/benedicte-blanc-68800044</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Galeries Lafayette</t>
+          <t>Michael Kors UAE</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>https://www.galerieslafayette.ae/</t>
+          <t>https://www.michaelkors.ae/</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Charbel Issa</t>
+          <t>Jessica Forshaw</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>General Manager, Galeries Lafayette Dubai</t>
+          <t>Head of Brand - Middle East Michael Kors, Chalhoub Group</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -9316,29 +9318,29 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/charbel-issa-20a43851</t>
+          <t>https://linkedin.com/in/jessica-forshaw-a390a148</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>American Eagle UAE (Alshaya Group)</t>
+          <t>Michael Kors UAE</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.ae/</t>
+          <t>https://www.michaelkors.ae/</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Caroline Nugent</t>
+          <t>Aden Nuh</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Senior Online Trading Manager - American Eagle, Alshaya Group</t>
+          <t>Digital Marketing Manager - Fashion (incl. Michael Kors), Chalhoub Group</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -9353,29 +9355,29 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/caroline-nugent-7342692b</t>
+          <t>https://linkedin.com/in/aden-nuh-50835214</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>American Eagle UAE (Alshaya Group)</t>
+          <t>Gymshark</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.ae/</t>
+          <t>https://www.gymshark.ae/</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Abdullah Nablaq</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Head of Online Trading, Alshaya Group</t>
+          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -9390,29 +9392,29 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/abdullah-nablaq</t>
+          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>American Eagle UAE (Alshaya Group)</t>
+          <t>Gymshark</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.ae/</t>
+          <t>https://www.gymshark.ae/</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Nour Salameh</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Digital Marketing Manager, Al Tayer Insignia (ex Bloomingdale's digital)</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -9427,29 +9429,29 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://linkedin.com/in/nour-salameh</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Galeries Lafayette</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>https://www.footlocker.ae/</t>
+          <t>https://www.galerieslafayette.ae/</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Adam Sharma</t>
+          <t>Charbel Issa</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Head of Online Trading &amp; Digital Marketing, Foot Locker &amp; New Balance MENA (Alshaya Group)</t>
+          <t>General Manager, Galeries Lafayette Dubai</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -9464,29 +9466,29 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gagansharma9</t>
+          <t>https://www.linkedin.com/in/charbel-issa-20a43851</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Bershka Kids</t>
+          <t>American Eagle UAE (Alshaya Group)</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/ae/</t>
+          <t>https://www.americaneagle.ae/</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Caroline Nugent</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
+          <t>Senior Online Trading Manager - American Eagle, Alshaya Group</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -9501,29 +9503,29 @@
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://www.linkedin.com/in/caroline-nugent-7342692b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Bershka Kids</t>
+          <t>American Eagle UAE (Alshaya Group)</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/ae/</t>
+          <t>https://www.americaneagle.ae/</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Mohammed Sajjad</t>
+          <t>Abdullah Nablaq</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
+          <t>Head of Online Trading, Alshaya Group</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -9538,29 +9540,29 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sajbhojani</t>
+          <t>https://www.linkedin.com/in/abdullah-nablaq</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Bershka Kids</t>
+          <t>American Eagle UAE (Alshaya Group)</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/ae/</t>
+          <t>https://www.americaneagle.ae/</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -9575,29 +9577,29 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Bershka Kids</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/ae/</t>
+          <t>https://www.footlocker.ae/</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Kassem Haidar</t>
+          <t>Adam Sharma</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
+          <t>Head of Online Trading &amp; Digital Marketing, Foot Locker &amp; New Balance MENA (Alshaya Group)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -9612,29 +9614,29 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
+          <t>https://www.linkedin.com/in/gagansharma9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Marks &amp; Spencer</t>
+          <t>Bershka Kids</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>https://www.marksandspencer.ae/en/fashion</t>
+          <t>https://www.bershka.com/ae/</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Yahya Obeid</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Head of Digital Marketing, Al-Futtaim (formerly Digital Marketing Lead M&amp;S MENA &amp; Asia)</t>
+          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -9649,29 +9651,29 @@
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/yahya-obeid</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Marks &amp; Spencer</t>
+          <t>Bershka Kids</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>https://www.marksandspencer.ae/en/fashion</t>
+          <t>https://www.bershka.com/ae/</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Ryan Dsouza</t>
+          <t>Mohammed Sajjad</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Digital Transformation - Marks &amp; Spencer Asia &amp; MENA, Al-Futtaim</t>
+          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -9686,29 +9688,29 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ryan-dsouza-40a49a2b</t>
+          <t>https://www.linkedin.com/in/sajbhojani</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Ted Baker.ae</t>
+          <t>Bershka Kids</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>https://tedbaker.ae/</t>
+          <t>https://www.bershka.com/ae/</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Yahya Obeid</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Head of Digital Marketing, Al-Futtaim (formerly Digital Marketing Lead M&amp;S MENA &amp; Asia)</t>
+          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -9723,29 +9725,29 @@
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/yahya-obeid</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Bershka Kids</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>https://shop.mango.com/ae/en</t>
+          <t>https://www.bershka.com/ae/</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Kassem Haidar</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
+          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -9760,29 +9762,29 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Marks &amp; Spencer</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>https://shop.mango.com/ae/en</t>
+          <t>https://www.marksandspencer.ae/en/fashion</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Mohammed Sajjad</t>
+          <t>Yahya Obeid</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
+          <t>Head of Digital Marketing, Al-Futtaim (formerly Digital Marketing Lead M&amp;S MENA &amp; Asia)</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -9797,29 +9799,29 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sajbhojani</t>
+          <t>https://linkedin.com/in/yahya-obeid</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Marks &amp; Spencer</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>https://shop.mango.com/ae/en</t>
+          <t>https://www.marksandspencer.ae/en/fashion</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Ryan Dsouza</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
+          <t>Digital Transformation - Marks &amp; Spencer Asia &amp; MENA, Al-Futtaim</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -9834,29 +9836,29 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://www.linkedin.com/in/ryan-dsouza-40a49a2b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Saint Laurent</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>https://shop.mango.com/ae/en</t>
+          <t>https://www.ysl.com/en-ae/</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Kassem Haidar</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
+          <t>VP, CDO - Omnichannel Digital Innovation, Al Tayer Insignia (Saint Laurent UAE franchise partner)</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -9871,29 +9873,29 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
+          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Massimo Dutti</t>
+          <t>Saint Laurent</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/ae/en/</t>
+          <t>https://www.ysl.com/en-ae/</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Khalid Al Tayer</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
+          <t>Managing Director Al Tayer Insignia &amp; CEO Ounass</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -9906,31 +9908,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Massimo Dutti</t>
+          <t>Ted Baker.ae</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/ae/en/</t>
+          <t>https://tedbaker.ae/</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Mohammed Sajjad</t>
+          <t>Yahya Obeid</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
+          <t>Head of Digital Marketing, Al-Futtaim (formerly Digital Marketing Lead M&amp;S MENA &amp; Asia)</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -9945,29 +9947,29 @@
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sajbhojani</t>
+          <t>https://linkedin.com/in/yahya-obeid</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Massimo Dutti</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/ae/en/</t>
+          <t>https://shop.mango.com/ae/en</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
+          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -9982,29 +9984,29 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Massimo Dutti</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/ae/en/</t>
+          <t>https://shop.mango.com/ae/en</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Kassem Haidar</t>
+          <t>Mohammed Sajjad</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
+          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -10019,29 +10021,29 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
+          <t>https://www.linkedin.com/in/sajbhojani</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Oysho</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/ae/</t>
+          <t>https://shop.mango.com/ae/en</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Sanaa Nazha</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Regional Brand Manager (Oysho), Azadea Group</t>
+          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -10056,29 +10058,29 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sanaa-nazha-b4618a33</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Oysho</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/ae/</t>
+          <t>https://shop.mango.com/ae/en</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Haniyyah Sasso</t>
+          <t>Kassem Haidar</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Brand Marketing Specialist (Oysho GCC/MENA), Azadea Group</t>
+          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -10093,29 +10095,29 @@
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/haniyyahsasso1</t>
+          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>boutiqaat</t>
+          <t>Massimo Dutti</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>https://www.boutiqaat.com/ar-ae/</t>
+          <t>https://www.massimodutti.com/ae/en/</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Abdullah Al-Julaibi</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO, Boutiqaat Group (leading UAE expansion)</t>
+          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -10128,31 +10130,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Armani  (incl. Armani Exchange)</t>
+          <t>Massimo Dutti</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>https://www.armani.com/en-ae/</t>
+          <t>https://www.massimodutti.com/ae/en/</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Mark Sinclair</t>
+          <t>Mohammed Sajjad</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>General Manager - Middle East, Giorgio Armani</t>
+          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -10167,29 +10169,29 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mark-sinclair-a0b9bb83</t>
+          <t>https://www.linkedin.com/in/sajbhojani</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Manyavar</t>
+          <t>Massimo Dutti</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>https://www.manyavar.com/en-ae/</t>
+          <t>https://www.massimodutti.com/ae/en/</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Paresh Anandapara</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>AGM Retail Business South 2 &amp; International (Manyavar &amp; Mohey incl. UAE), Vedant Fashions</t>
+          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -10204,29 +10206,29 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pareshanandapara</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Manyavar</t>
+          <t>Massimo Dutti</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>https://www.manyavar.com/en-ae/</t>
+          <t>https://www.massimodutti.com/ae/en/</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Darshan Kothari</t>
+          <t>Kassem Haidar</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Operations Manager - Manyavar MENA</t>
+          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -10241,29 +10243,29 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/darshan-kothari-5377ab141</t>
+          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Nayomi (Jamjoom Fashion)</t>
+          <t>Oysho</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>https://ae.nayomi.com/</t>
+          <t>https://www.oysho.com/ae/</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Natalija Karavajeva</t>
+          <t>Sanaa Nazha</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Director of Ecommerce and Digital Strategy (Nayomi), Jamjoom Fashion</t>
+          <t>Regional Brand Manager (Oysho), Azadea Group</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -10278,29 +10280,29 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/natalija-karavajeva</t>
+          <t>https://www.linkedin.com/in/sanaa-nazha-b4618a33</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>Nayomi (Jamjoom Fashion)</t>
+          <t>Oysho</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>https://ae.nayomi.com/</t>
+          <t>https://www.oysho.com/ae/</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Sidrah Ahmed</t>
+          <t>Haniyyah Sasso</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Ecommerce and Digital Marketing Manager - Nayomi, Jamjoom Fashion</t>
+          <t>Brand Marketing Specialist (Oysho GCC/MENA), Azadea Group</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -10315,29 +10317,29 @@
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sidrah-ahmed-124129a8</t>
+          <t>https://www.linkedin.com/in/haniyyahsasso1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Nayomi (Jamjoom Fashion)</t>
+          <t>boutiqaat</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>https://ae.nayomi.com/</t>
+          <t>https://www.boutiqaat.com/ar-ae/</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Osman Jamjoom</t>
+          <t>Abdullah Al-Julaibi</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Transformation Director (technology, digital development), Jamjoom Fashion</t>
+          <t>Co-Founder &amp; CEO, Boutiqaat Group (leading UAE expansion)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -10350,31 +10352,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/osman-jamjoom-ab3984a7</t>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Stradivarius</t>
+          <t>Armani  (incl. Armani Exchange)</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/ae/</t>
+          <t>https://www.armani.com/en-ae/</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Mark Sinclair</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
+          <t>General Manager - Middle East, Giorgio Armani</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -10389,29 +10391,29 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://www.linkedin.com/in/mark-sinclair-a0b9bb83</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Stradivarius</t>
+          <t>Manyavar</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/ae/</t>
+          <t>https://www.manyavar.com/en-ae/</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Mohammed Sajjad</t>
+          <t>Paresh Anandapara</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
+          <t>AGM Retail Business South 2 &amp; International (Manyavar &amp; Mohey incl. UAE), Vedant Fashions</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -10426,29 +10428,29 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sajbhojani</t>
+          <t>https://www.linkedin.com/in/pareshanandapara</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>Stradivarius</t>
+          <t>Manyavar</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/ae/</t>
+          <t>https://www.manyavar.com/en-ae/</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Darshan Kothari</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
+          <t>Operations Manager - Manyavar MENA</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -10463,29 +10465,29 @@
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://www.linkedin.com/in/darshan-kothari-5377ab141</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Stradivarius</t>
+          <t>Nayomi (Jamjoom Fashion)</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/ae/</t>
+          <t>https://ae.nayomi.com/</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Kassem Haidar</t>
+          <t>Natalija Karavajeva</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
+          <t>Director of Ecommerce and Digital Strategy (Nayomi), Jamjoom Fashion</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -10500,29 +10502,29 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
+          <t>https://www.linkedin.com/in/natalija-karavajeva</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>GAP</t>
+          <t>Nayomi (Jamjoom Fashion)</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>https://www.gap.ae/</t>
+          <t>https://ae.nayomi.com/</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Sumit Srivastava</t>
+          <t>Sidrah Ahmed</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
+          <t>Ecommerce and Digital Marketing Manager - Nayomi, Jamjoom Fashion</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -10537,29 +10539,29 @@
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
+          <t>https://www.linkedin.com/in/sidrah-ahmed-124129a8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GAP</t>
+          <t>Nayomi (Jamjoom Fashion)</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>https://www.gap.ae/</t>
+          <t>https://ae.nayomi.com/</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nour Salameh</t>
+          <t>Osman Jamjoom</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager, Al Tayer Insignia (ex Bloomingdale's digital)</t>
+          <t>Transformation Director (technology, digital development), Jamjoom Fashion</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10574,29 +10576,29 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/nour-salameh</t>
+          <t>https://www.linkedin.com/in/osman-jamjoom-ab3984a7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Nishat Linen UAE (Nishat Linen Trading LLC)</t>
+          <t>Stradivarius</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>https://www.nishatlinenuae.com/</t>
+          <t>https://www.stradivarius.com/ae/</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Mohammad Shahzad</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Global E-Commerce Manager, Nishat Linen (launched/runs UAE online store)</t>
+          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -10611,29 +10613,29 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohammad-shahzad-90904398</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Nishat Linen UAE (Nishat Linen Trading LLC)</t>
+          <t>Stradivarius</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>https://www.nishatlinenuae.com/</t>
+          <t>https://www.stradivarius.com/ae/</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Sohail Akram</t>
+          <t>Mohammed Sajjad</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Retail Operations Manager, Nishat Linen Trading LLC (UAE)</t>
+          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10648,29 +10650,29 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sohail-akram-a06bba16</t>
+          <t>https://www.linkedin.com/in/sajbhojani</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Lefties</t>
+          <t>Stradivarius</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>https://www.lefties.com/ae/</t>
+          <t>https://www.stradivarius.com/ae/</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Mariam Gviniashvili</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Brand Manager, Lefties (Dubai)</t>
+          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -10685,29 +10687,29 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mariam-gviniashvili-861b03128</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Stradivarius</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>https://giordano.ae/</t>
+          <t>https://www.stradivarius.com/ae/</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Ishwar Chugani</t>
+          <t>Kassem Haidar</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Managing Director at Giordano</t>
+          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -10722,29 +10724,29 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ishwarchugani</t>
+          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear</t>
+          <t>GAP</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/ae/</t>
+          <t>https://www.gap.ae/</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
+          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -10759,29 +10761,29 @@
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear</t>
+          <t>GAP</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/ae/</t>
+          <t>https://www.gap.ae/</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Mohammed Sajjad</t>
+          <t>Nour Salameh</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
+          <t>Digital Marketing Manager, Al Tayer Insignia (ex Bloomingdale's digital)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -10796,29 +10798,29 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sajbhojani</t>
+          <t>https://linkedin.com/in/nour-salameh</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear</t>
+          <t>Balenciaga</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/ae/</t>
+          <t>https://www.balenciaga.com/en-ae/</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
+          <t>VP, CDO - Omnichannel Digital Innovation, Al Tayer Insignia (Balenciaga UAE franchise partner)</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -10833,29 +10835,29 @@
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear</t>
+          <t>Nishat Linen UAE (Nishat Linen Trading LLC)</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/ae/</t>
+          <t>https://www.nishatlinenuae.com/</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Kassem Haidar</t>
+          <t>Mohammad Shahzad</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
+          <t>Global E-Commerce Manager, Nishat Linen (launched/runs UAE online store)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -10870,29 +10872,29 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
+          <t>https://www.linkedin.com/in/mohammad-shahzad-90904398</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>Matalan Middle East (BTC Fashion)</t>
+          <t>Nishat Linen UAE (Nishat Linen Trading LLC)</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>https://www.matalanme.com/ae_en/</t>
+          <t>https://www.nishatlinenuae.com/</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Mufid Samo</t>
+          <t>Sohail Akram</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Country Manager UAE, BTC Fashion - Matalan Middle East</t>
+          <t>Retail Operations Manager, Nishat Linen Trading LLC (UAE)</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -10907,29 +10909,29 @@
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mufid-samo-a3962b7b</t>
+          <t>https://www.linkedin.com/in/sohail-akram-a06bba16</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RUNNERS SPORTS</t>
+          <t>Lefties</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>https://runners.ae/</t>
+          <t>https://www.lefties.com/ae/</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Benyamin K.</t>
+          <t>Mariam Gviniashvili</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Managing Director, Runner's Sports UAE</t>
+          <t>Brand Manager, Lefties (Dubai)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -10944,29 +10946,29 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/benkhademi</t>
+          <t>https://www.linkedin.com/in/mariam-gviniashvili-861b03128</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Styli (Landmark Group)</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>https://stylishop.com/ae/</t>
+          <t>https://giordano.ae/</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Shibu Tharakan</t>
+          <t>Ishwar Chugani</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, Styli (Landmark Group)</t>
+          <t>Managing Director at Giordano</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -10981,29 +10983,29 @@
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/shibutharakan</t>
+          <t>https://www.linkedin.com/in/ishwarchugani</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Muji</t>
+          <t>Club L London</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>https://www.muji.ae/</t>
+          <t>https://www.clubllondon.ae/</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Mridumesh Kumar Rai</t>
+          <t>Nikita Shetye</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Business Director - NEXT / MUJI / Claire's / Disney Store (MENA), Alshaya Group</t>
+          <t>General Manager - GCC eCommerce, Club L London (Dubai)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -11018,29 +11020,29 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mridumesh</t>
+          <t>https://linkedin.com/in/nikita-shetye-3294a8a5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>SQUATWOLF</t>
+          <t>Club L London</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>https://squatwolf.com/</t>
+          <t>https://www.clubllondon.ae/</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Wajdan Gul</t>
+          <t>Annabel Randev</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Founder &amp; Co-CEO at SQUATWOLF</t>
+          <t>ME Marketing Manager, Club L London (Dubai)</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -11055,29 +11057,29 @@
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/wajdan</t>
+          <t>https://linkedin.com/in/annabel-randev-305b7317a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>SQUATWOLF</t>
+          <t>Club L London</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>https://squatwolf.com/</t>
+          <t>https://www.clubllondon.ae/</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Anam Khalid</t>
+          <t>Katie Randev</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; Co-CEO @SQUATWOLF</t>
+          <t>Founder and CEO, Club L London (Manchester, UK)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11092,29 +11094,29 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/anam-khalid</t>
+          <t>https://linkedin.com/in/katie-randev-716986129</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Pull&amp;Bear</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>https://www.reebok.ae/</t>
+          <t>https://www.pullandbear.com/ae/</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Vishal VijayKumar</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Head of Omnichannel, Al Boom Marine (Reebok UAE operator)</t>
+          <t>Regional Head of eCommerce, Omnichannel &amp; AI Digital Transformation, Azadea Group (UAE franchise operator)</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -11127,31 +11129,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Pull&amp;Bear</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>https://www.reebok.ae/</t>
+          <t>https://www.pullandbear.com/ae/</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Mohd Faraz</t>
+          <t>Mohammed Sajjad</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Brand Specialist (Reebok.ae, Beyond the Beach)</t>
+          <t>VP Marketing and Digital (CMO/CDO), Azadea Group</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -11166,29 +11168,29 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohd-faraz-aa7b421aa</t>
+          <t>https://www.linkedin.com/in/sajbhojani</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Pull&amp;Bear</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>https://www.reebok.ae/</t>
+          <t>https://www.pullandbear.com/ae/</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Ahmed Abdelmaaboud</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>E-commerce Operations Executive (Reebok UAE &amp; KSA), Al Boom Marine</t>
+          <t>Head of Marketing &amp; Business Development MENA, Azadea Group (Zara, Massimo Dutti, Adidas, Decathlon)</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -11203,29 +11205,29 @@
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ahmed-abdelmaaboud-a23a3892</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Kashkha</t>
+          <t>Pull&amp;Bear</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>https://www.kashkha.com/</t>
+          <t>https://www.pullandbear.com/ae/</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Dharam Raheja</t>
+          <t>Kassem Haidar</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner at Kashkha كشخة</t>
+          <t>Regional E-Commerce Omni Trading Manager, Azadea Group</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -11240,29 +11242,29 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/dharam-raheja-a73611ba</t>
+          <t>https://www.linkedin.com/in/kassem-haidar-58ba1549</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>Kashkha</t>
+          <t>Matalan Middle East (BTC Fashion)</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>https://www.kashkha.com/</t>
+          <t>https://www.matalanme.com/ae_en/</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Roshan kushalvardhan</t>
+          <t>Mufid Samo</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>E-commerce Manager at Kashkha كشخة</t>
+          <t>Country Manager UAE, BTC Fashion - Matalan Middle East</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -11277,29 +11279,29 @@
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/roshan-kushalvardhan-81168671</t>
+          <t>https://www.linkedin.com/in/mufid-samo-a3962b7b</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Kiabi</t>
+          <t>Valentino (Middle East)</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>https://www.kiabi.ae/</t>
+          <t>https://www.valentino.com/en-ae/</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Yahya Obeid</t>
+          <t>Zahiya Hassan Tawil</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Head of Digital Marketing, Al-Futtaim (formerly Digital Marketing Lead M&amp;S MENA &amp; Asia)</t>
+          <t>Head of Marketing and Communications, Valentino (Dubai)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -11314,29 +11316,29 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/yahya-obeid</t>
+          <t>https://linkedin.com/in/zahiya-hassan-tawil-a7428423</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>CHIC LE FRIQUE</t>
+          <t>Valentino (Middle East)</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>https://chiclefrique.com/</t>
+          <t>https://www.valentino.com/en-ae/</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Sara Rahbari</t>
+          <t>Thibault Hesse</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Founder at Chic Le Frique</t>
+          <t>Chief Executive Officer - Middle East, Africa and India, Valentino</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -11351,19 +11353,19 @@
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sara-rahbari-4b817338</t>
+          <t>https://linkedin.com/in/thibault-hesse-58b210144</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Cotton On</t>
+          <t>Adventure HQ</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>https://cottonon.ae/</t>
+          <t>https://adventurehq.ae/</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -11373,7 +11375,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Marketing Lead (Cotton On, Forever 21, Typo, Adventure HQ), Sharaf Retail</t>
+          <t>Marketing Lead (Sharaf Retail - Adventure HQ, Adventure Zone and other brands)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -11395,22 +11397,22 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>Cotton On</t>
+          <t>RUNNERS SPORTS</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>https://cottonon.ae/</t>
+          <t>https://runners.ae/</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Vaibhav Garg</t>
+          <t>Benyamin K.</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>E-Commerce &amp; Business Excellence Manager, Sharaf Retail Group</t>
+          <t>Managing Director, Runner's Sports UAE</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -11423,31 +11425,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benkhademi</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>JACK &amp; JONES</t>
+          <t>Tory Burch</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>https://www.jackjones.com/ar-ae/</t>
+          <t>https://www.toryburch.ae/</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Hui Runge</t>
+          <t>Patrick McMahon</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Country Brand Manager JACK &amp; JONES Middle East &amp; Emerging Markets, BESTSELLER Region East</t>
+          <t>Ecommerce Lead - Tory Burch, Chalhoub Group (Dubai)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -11462,29 +11464,29 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hui-runge-5abb42161</t>
+          <t>https://linkedin.com/in/patrickmcmahon5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>JACK &amp; JONES</t>
+          <t>Styli (Landmark Group)</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>https://www.jackjones.com/ar-ae/</t>
+          <t>https://stylishop.com/ae/</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Nitish Pandey</t>
+          <t>Shibu Tharakan</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>Retail Business Partner - JACK &amp; JONES, BESTSELLER</t>
+          <t>Chief Executive Officer, Styli (Landmark Group)</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -11499,29 +11501,29 @@
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nitish-pandey2015</t>
+          <t>https://www.linkedin.com/in/shibutharakan</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>YOOX</t>
+          <t>Maison Margiela UAE</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>https://www.yoox.com/ae/</t>
+          <t>https://www.maisonmargiela.ae/</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Shayma Emam</t>
+          <t>Ilaria Manzi</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Head of ME Commercial Performance, NET-A-PORTER (YOOX NET-A-PORTER)</t>
+          <t>Digital Manager (Maison Margiela, Marni, Jil Sander - OTB/Chalhoub JV), OTB</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -11536,29 +11538,29 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/shayma-emam-7a68a4159</t>
+          <t>https://linkedin.com/in/ilaria-manzi</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>StudioSuits (Harry Fashion)</t>
+          <t>Muji</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>https://www.studiosuits.com/</t>
+          <t>https://www.muji.ae/</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Haresh Shahari</t>
+          <t>Mridumesh Kumar Rai</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>Founder, Harry Fashion (operator of StudioSuits) / Partner Harry Fashion LLP</t>
+          <t>Business Director - NEXT / MUJI / Claire's / Disney Store (MENA), Alshaya Group</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -11573,29 +11575,29 @@
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/haresh-shahari-2458a2a</t>
+          <t>https://www.linkedin.com/in/mridumesh</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Bally</t>
+          <t>The Giving Movement</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>https://www.bally.ae/</t>
+          <t>https://thegivingmovement.com/</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Ahmed Ismail</t>
+          <t>Rania Masri El Khatib</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of E-Commerce, Jashanmal Group</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -11608,31 +11610,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ahmed-ismail-899350a2</t>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Bally</t>
+          <t>SQUATWOLF</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>https://www.bally.ae/</t>
+          <t>https://squatwolf.com/</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Bismil Razik</t>
+          <t>Wajdan Gul</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager, Jashanmal Group</t>
+          <t>Founder &amp; Co-CEO at SQUATWOLF</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -11647,29 +11649,29 @@
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/bismilrazik</t>
+          <t>https://www.linkedin.com/in/wajdan</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>TennisShop.ae</t>
+          <t>SQUATWOLF</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>https://www.tennisshop.ae/</t>
+          <t>https://squatwolf.com/</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sagar Sharma</t>
+          <t>Anam Khalid</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, TennisShop.ae | Strategic</t>
+          <t>Founder &amp; Co-CEO @SQUATWOLF</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -11684,29 +11686,29 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sagarsharma-tennis</t>
+          <t>https://www.linkedin.com/in/anam-khalid</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>Endless</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>https://endless.ae/</t>
+          <t>https://www.reebok.ae/</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Rosie Gunn</t>
+          <t>Vishal VijayKumar</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO of Endless</t>
+          <t>Head of Omnichannel, Al Boom Marine (Reebok UAE operator)</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -11719,31 +11721,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/rosiegunn1</t>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>CNCPTS</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>https://cncpts.ae/</t>
+          <t>https://www.reebok.ae/</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Bibek Karki</t>
+          <t>Mohd Faraz</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Managing Brand @ CNCPTS Dubai (Brand Strategy, Buying, Retail)</t>
+          <t>Ecommerce Brand Specialist (Reebok.ae, Beyond the Beach)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -11758,49 +11760,2898 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/kbibek82</t>
+          <t>https://www.linkedin.com/in/mohd-faraz-aa7b421aa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
+          <t>Reebok</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>https://www.reebok.ae/</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Ahmed Abdelmaaboud</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Operations Executive (Reebok UAE &amp; KSA), Al Boom Marine</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ahmed-abdelmaaboud-a23a3892</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Kashkha</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kashkha.com/</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Dharam Raheja</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner at Kashkha كشخة</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dharam-raheja-a73611ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>Kashkha</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kashkha.com/</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Roshan kushalvardhan</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Manager at Kashkha كشخة</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roshan-kushalvardhan-81168671</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Reiss UAE (Jashanmal Group)</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reiss.com/ae/en</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Ismail</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Regional Head of E-Commerce, Jashanmal Group</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ahmed-ismail-899350a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>Reiss UAE (Jashanmal Group)</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>https://www.reiss.com/ae/en</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>Shuja Jashanmal</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>Partner &amp; CEO, Jashanmal Group</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shujajashanmal</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Kiabi</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kiabi.ae/</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Yahya Obeid</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Head of Digital Marketing, Al-Futtaim (formerly Digital Marketing Lead M&amp;S MENA &amp; Asia)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/yahya-obeid</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>CAS Abaya (Crystal Abaya Studio)</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>https://casbasics.com/</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Maryam Karim</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>CEO, Crystal Abaya Studio (CAS Abaya)</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>CAS Abaya (Crystal Abaya Studio)</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>https://casbasics.com/</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Muhammad Adnan Shaheen</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce and Digital Marketing Specialist, Crystal Abaya Studio</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/muhammad-adnan-shaheen</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>GANT UAE (Liwa Trading Enterprises)</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>https://gant.ae/</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Rebecca Holland</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>Head of Digital, Liwa Trading Enterprises (GANT UAE operator)</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rebecca-holland-1110b178</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Off-White UAE</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.off---white.com/en-ae/</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Maria ElKheyami</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager - omni-channel fashion franchise (incl. Off-White), Chalhoub Group</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/maria-elkheyami-b0822852</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>Columbia UAE</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>https://columbia.ae/</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>Vinay Banga</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>Head of Brand (Columbia, GCC &amp; SEA), GMG</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/vinay-banga</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Max Mara UAE</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.maxmara.ae/</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Kenza Bouzoubaa</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Regional E-commerce Manager, Max Mara Fashion Group (Dubai)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/kenza-bouzoubaa-920b3035</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>Max Mara UAE</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>https://www.maxmara.ae/</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>Aden Nuh</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager - Fashion (incl. Max Mara), Chalhoub Group</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/aden-nuh-50835214</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>HUGO BOSS UAE</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>https://hugoboss.ae/</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Alessandro Bovone</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Omnichannel Senior Manager EMR+ (eCommerce &amp; Digital), HUGO BOSS</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/alessandro-bovone-4a7976142</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>HUGO BOSS UAE</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>https://hugoboss.ae/</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>Dina Eid</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Manager, HUGO BOSS (Dubai)</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dina-eid</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>COS UAE</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>https://ae.cos.com/en/</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Hema Subramanian</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Senior Manager - Performance Marketing &amp; Ecommerce P&amp;L, H&amp;M / COS / Victoria's Secret (Alshaya Group)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/shemalathadigitalmarketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>COS UAE</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>https://ae.cos.com/en/</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>Kalpna Chaturvedi</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager - eCommerce &amp; Marketing (H&amp;M, COS and 20+ brands), Alshaya Group</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/kalpnachaturvedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>COS UAE</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>https://ae.cos.com/en/</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Isah Hamisu Isah</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Content &amp; Onsite Marketing Manager - H&amp;M COS Web &amp; App (Alshaya Group)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/isahhamisu</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>Maria.B. Designs (AE)</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mariab.ae/</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Hammad Sohail</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>Chief Marketing &amp; Strategy Officer, Maria.B. Designs</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hammad-sohail-31893838</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Tryano</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tryano.com/</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Muhammad Hamza Muzaffar</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Head of eCommerce &amp; Digital (Tryano), Chalhoub Group</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hamzamuzaffar1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>Tryano</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tryano.com/</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>Reda Keddaji</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>General Manager, Tryano (Chalhoub Group)</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reda-keddaji-b8990235</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Maje UAE Official Site</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>https://www.maje.ae/</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Rema Nelson</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>General Manager, Fashion MENA (Maje, Sandro, Kiabi, Ted Baker, Aape), Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>Suitsupply UAE</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>https://suitsupply.com/en-ae/</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Shames Al Hashemi</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>Managing Director, Dual Investments LLC (Suitsupply UAE franchise operator)</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/shames-mohamed-al-sharif-al-hashemi-34a8231a</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Suitsupply UAE</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>https://suitsupply.com/en-ae/</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Baum</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>VP E-Commerce and Growth, Suitsupply (global, Helsinki-based)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>https://fi.linkedin.com/in/fabio-baum-b9458a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>La Senza UAE (Liwa Trading Enterprises)</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lasenza.com/ae/</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>Kunal Singh</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>Head of Digital Commerce &amp; Transformation, Liwa Trading Enterprises (La Senza UAE franchise operator)</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/kunal-singh-digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Diesel UAE</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>https://ae.diesel.com/</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Tarek Barakat</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; E-commerce Director, Beside Group (Diesel Middle East partner)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/tarek-barakat-23b83132</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>Allbirds | UAE Official Store</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>https://allbirds.ae/</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>Phillip Smith</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (Allbirds and other brands)</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/phillip-smith-9aa91a44</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>DKNY | UAE Official Store</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>https://dkny.ae/</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Phillip Smith</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (DKNY and other brands)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/phillip-smith-9aa91a44</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>DKNY | UAE Official Store</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>https://dkny.ae/</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Magui Daher</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>Regional Brand Manager - DKNY &amp; Donna Karan New York (Middle East), Alyasra Fashion</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/magui-daher-5b95a584</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Online Fashion Store For Women: Etoile La Boutique</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etoilelaboutique.com/en-ae/</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Ingie Chalhoub</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Founder and President, Etoile Group (Etoile La Boutique)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>CHIC LE FRIQUE</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>https://chiclefrique.com/</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>Sara Rahbari</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>Founder at Chic Le Frique</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sara-rahbari-4b817338</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Lacoste UAE</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lacoste.com/ae/</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Sara AlQenaei</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Regional Marketing Manager - Lacoste Middle East, Chalhoub Group</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sara-alqenaei-30b347b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>Lacoste UAE</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lacoste.com/ae/</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>Aden Nuh</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager - Fashion (incl. Lacoste, Michael Kors, Max Mara), Chalhoub Group</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/aden-nuh-50835214</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Cotton On</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>https://cottonon.ae/</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Imran K.</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Lead (Cotton On, Forever 21, Typo, Adventure HQ), Sharaf Retail</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/imrankapadia-growth-and-digital-performance-marketing-expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>Cotton On</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>https://cottonon.ae/</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>Vaibhav Garg</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>E-Commerce &amp; Business Excellence Manager, Sharaf Retail Group</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>JACK &amp; JONES</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jackjones.com/ar-ae/</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Hui Runge</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Country Brand Manager JACK &amp; JONES Middle East &amp; Emerging Markets, BESTSELLER Region East</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hui-runge-5abb42161</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>JACK &amp; JONES</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>https://www.jackjones.com/ar-ae/</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Nitish Pandey</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>Retail Business Partner - JACK &amp; JONES, BESTSELLER</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nitish-pandey2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>YOOX</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yoox.com/ae/</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Shayma Emam</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Head of ME Commercial Performance, NET-A-PORTER (YOOX NET-A-PORTER)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shayma-emam-7a68a4159</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Golf Superstore UAE (Prosports International LLC)</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>https://www.golfsuperstore.ae/</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Stuart Taylor</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>General Manager (PGA Professional), Prosports International - Golf Superstore</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Golf Superstore UAE (Prosports International LLC)</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>https://www.golfsuperstore.ae/</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Ara Nakhnikian</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Owner, Prosports International LLC (Golf Superstore)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Golf Superstore UAE (Prosports International LLC)</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>https://www.golfsuperstore.ae/</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Jai Khandelwal</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>COO, Prosports International LLC</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Golf Superstore UAE (Prosports International LLC)</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>https://www.golfsuperstore.ae/</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>HH Sheikh Saeed Mohamed Hasher Al Maktoum</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Owner, Prosports International LLC</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>eGolf Megastore</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>https://www.egolfmegastore.ae/</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>Dean Cheesley</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>CEO &amp; Founder, eGolf Megastore</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dean-cheesley-13949114</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>eGolf Megastore</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>https://www.egolfmegastore.ae/</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Amrita Thakur</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Coordinator, eGolf Megastore</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/amrita-thakur-b5a44746</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>Posh Abaya</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>https://www.poshabaya.ae/</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>Waleed Ali Mousa</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>Creative Director, Posh Abaya</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>Waleed@poshabaya.ae</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/waleed-ali-mousa-137a2927</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>StudioSuits (Harry Fashion)</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.studiosuits.com/</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Haresh Shahari</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Founder, Harry Fashion (operator of StudioSuits) / Partner Harry Fashion LLP</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/haresh-shahari-2458a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>Bally</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>https://www.bally.ae/</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>Ahmed Ismail</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>Regional Head of E-Commerce, Jashanmal Group</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ahmed-ismail-899350a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Bally</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bally.ae/</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Bismil Razik</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager, Jashanmal Group</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bismilrazik</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>LC Waikiki UAE</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lcwaikiki.com/en-AE</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>Ashwani Saklani</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>Senior Marketing Manager (Crocs, Aeropostale, LC Waikiki; e-commerce marketing), Apparel Group</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/ashwani-saklani-21408058</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>LC Waikiki UAE</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lcwaikiki.com/en-AE</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Abdelrahman A. Hamada</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Digital and Growth Marketing Lead, LC Waikiki (Dubai)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>TennisShop.ae</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tennisshop.ae/</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>Sagar Sharma</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO, TennisShop.ae | Strategic</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sagarsharma-tennis</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Karl Lagerfeld UAE</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>https://www.karllagerfeld.com/en-ae/</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Keeman Au</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Director of E-Commerce, KARL LAGERFELD</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/keemanau</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>Karl Lagerfeld UAE</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>https://www.karllagerfeld.com/en-ae/</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>James Pollak</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>Director of E-Commerce Operations, KARL LAGERFELD</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>https://endless.ae/</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Rosie Gunn</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO of Endless</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rosiegunn1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>AMRI Fashions LLC (amri.ae), Ajman</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>https://amri.ae/</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>Darshak Jayesh Khandhar</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>Head of E-commerce Business Development - B2B &amp; Private Labels, Amri Fashions (remote, Canada)</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/darshak-jayesh-khandhar-858050209</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>AMRI Fashions LLC (amri.ae), Ajman</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>https://amri.ae/</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Nirav Bhagat</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>General Manager Operations, Amri Fashions</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nirav-bhagat-4365ba39</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>AMRI Fashions LLC (amri.ae), Ajman</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>https://amri.ae/</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>Ashar Qazi</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>Head of Retail Business, Amri Fashions</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/asharqazi</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>BATIK - AE</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>https://batik.ae/</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Mustahsin Qamar</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Director, BATIK (Dubai-based)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mustahsin-qamar-a4676028</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>BATIK - AE</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>https://batik.ae/</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>Hammad Latif</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>Head of E-commerce, BATIK (group, Islamabad)</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hammad-latif-82427aab</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>CNCPTS</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>https://cncpts.ae/</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Bibek Karki</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Managing Brand @ CNCPTS Dubai (Brand Strategy, Buying, Retail)</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/kbibek82</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>Ipekyol UAE</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>https://ae.ipekyol.com/</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>Erkal Ceyhan</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>Director of Ecommerce, Ipekyol Group (runs ae.ipekyol.com)</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/erkalceyhan</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>ELIE SAAB</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>https://eliesaab.com/</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Yazan Ashkar</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Global CRM Director, ELIE SAAB (Dubai)</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/yazanashkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>JD Sports UAE</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>https://www.jdsports.ae/</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>Candice de Dieuleveult</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>Director of Ecommerce, GMG (operator of JD Sports Middle East)</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/candice-de-dieuleveult-9139a0135</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>JD Sports UAE</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jdsports.ae/</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Rahul Singh Negi</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Head of Category, JD Sports (UAE, KSA, Qatar, Bahrain, Egypt)</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/rahul-singh-negi-92218031b</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lifestyleshops.com/ae/</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>Rahul Jagtiani</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>Group Director - Digital (leads e-commerce, IT, analytics, loyalty), Landmark Group</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lifestyleshops.com/ae/</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Ashick Ali</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Vice President and Head of E-Commerce, Landmark Group (Head of Ecommerce, Homebox)</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aliashick</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lifestyleshops.com/ae/</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>Aditya Choudhary</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>Head of Digital Marketing &amp; CRM, Landmark Group</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adityakc14</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
           <t>VAVCI</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B214" s="3" t="inlineStr">
         <is>
           <t>https://vavci.ae/</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
         <is>
           <t>KANIKA Mehra</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Business Owner at vavci</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F147" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/kanika-mehra-9b063b2a5</t>
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Shop Sported Triathlon Dubai: One-stop shop for all things Triathlon</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sported.ae/</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>David Hunt</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>Co-Owner, Sported.ae</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>D'S DAMAT ONLINE</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dsdamatonline.ae/</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Muhammed Hashim</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Omni Channel Manager (E-commerce &amp; Marketing for D'S Damat &amp; Damat Tween UAE), Nahr Al Madeena Trading LLC</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/muhammed-hashim-b32611117</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Triumph Underwear</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>https://triumph.ae/</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>Phillip Smith</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (Triumph and other brands)</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/phillip-smith-9aa91a44</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>RR Cellars LLC</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>https://rrcellars.ae/</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Rishi Udainiya</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager, RR Cellars LLC</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/rishi-udainiya-79555094</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>DeFacto UAE</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>https://www.defacto.com/en-ae</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>Ahmed Abuelela</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>International E-Commerce Director - MENA &amp; CIS, DeFacto (Istanbul)</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/aabuelela</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>DeFacto UAE</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>https://www.defacto.com/en-ae</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Goncagül Düzen Akyıldız</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>International E-Commerce Unit Manager MENA &amp; CIS, DeFacto</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/goncag%C3%BCl-d%C3%BCzen</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>Habayeb Abaya Shop</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>https://habayeb.com/</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>Seifollah Nouraei</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>Owner and CEO, Habayeb</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G221" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Official Liverpool FC Store Middle East</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>https://store.liverpoolfc.ae/</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Muhammed Sagar</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Digital &amp; E-Commerce Lead (Head of Digital), Seventy8 Sports Trading LLC - Official Liverpool FC Store Middle East</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/muhammed-sagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>Official Liverpool FC Store Middle East</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>https://store.liverpoolfc.ae/</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>Geoff Kershaw</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; Managing Director, Seventy8 Sports Trading LLC</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G223" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Official Liverpool FC Store Middle East</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>https://store.liverpoolfc.ae/</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Sophie Holmes</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Group Head of Marketing, Seventy8 Sports Trading LLC</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G147"/>
+  <autoFilter ref="A1:G224"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -11912,13 +14763,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId120"/>
@@ -11942,8 +14793,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId145"/>
@@ -11983,18 +14834,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId196"/>
@@ -12006,48 +14857,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId247"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId249"/>
@@ -12063,26 +14914,164 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId259"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId271"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId273"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId275"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B205" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B206" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B207" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B208" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B209" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B211" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B212" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B213" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B214" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B215" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B216" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B217" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B218" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B219" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B220" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B221" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B222" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B223" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B224" r:id="rId419"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
